--- a/data/2026/employers_2026.xlsx
+++ b/data/2026/employers_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naughtm\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF232D6-3A4F-40C2-9F18-3A89FC01708A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A797FB3B-C7D3-49EC-B144-0A429ED6CCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="795" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -12710,9 +12710,6 @@
     <t>Zyte Group Limited</t>
   </si>
   <si>
-    <t xml:space="preserve">Employer Name </t>
-  </si>
-  <si>
     <t>Permits Issued Jan</t>
   </si>
   <si>
@@ -12726,6 +12723,9 @@
   </si>
   <si>
     <t>Permits Issued Apr</t>
+  </si>
+  <si>
+    <t>Employer Name</t>
   </si>
 </sst>
 </file>
@@ -13144,22 +13144,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="60">
       <c r="A1" s="3" t="s">
+        <v>4230</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>4225</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>4226</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>4227</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>4229</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4228</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4230</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>4229</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -75924,6 +75924,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="199" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="f29b0ff1a26a7575c948acee1be83c00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3fe347a261331acec84421138fd81903" ns2:_="">
     <xsd:import namespace="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
@@ -76132,15 +76141,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -76181,6 +76181,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671879E3-B982-4FE4-BADD-85A07701A750}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7A7B58-26E5-466B-854F-C9D5FAFB5E44}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -76194,14 +76202,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671879E3-B982-4FE4-BADD-85A07701A750}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/2026/employers_2026.xlsx
+++ b/data/2026/employers_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A797FB3B-C7D3-49EC-B144-0A429ED6CCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52089A1B-B3CB-4AB1-92CD-1D8F4EA013B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75902,18 +75902,10 @@
       <c r="A4226" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4226" s="5">
-        <v>3204</v>
-      </c>
-      <c r="C4226" s="5">
-        <v>2789</v>
-      </c>
-      <c r="D4226" s="5">
-        <v>2904</v>
-      </c>
-      <c r="E4226" s="5">
-        <v>3322</v>
-      </c>
+      <c r="B4226" s="5"/>
+      <c r="C4226" s="5"/>
+      <c r="D4226" s="5"/>
+      <c r="E4226" s="5"/>
       <c r="F4226" s="5">
         <v>12219</v>
       </c>
@@ -75924,15 +75916,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="199" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="f29b0ff1a26a7575c948acee1be83c00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3fe347a261331acec84421138fd81903" ns2:_="">
     <xsd:import namespace="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
@@ -76141,6 +76124,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -76181,14 +76173,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671879E3-B982-4FE4-BADD-85A07701A750}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7A7B58-26E5-466B-854F-C9D5FAFB5E44}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -76202,6 +76186,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671879E3-B982-4FE4-BADD-85A07701A750}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/2026/employers_2026.xlsx
+++ b/data/2026/employers_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52089A1B-B3CB-4AB1-92CD-1D8F4EA013B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DB9644-46B7-4946-B909-A3BBAE9C78B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -75902,10 +75902,18 @@
       <c r="A4226" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4226" s="5"/>
-      <c r="C4226" s="5"/>
-      <c r="D4226" s="5"/>
-      <c r="E4226" s="5"/>
+      <c r="B4226" s="5">
+        <v>3204</v>
+      </c>
+      <c r="C4226" s="5">
+        <v>2789</v>
+      </c>
+      <c r="D4226" s="5">
+        <v>2904</v>
+      </c>
+      <c r="E4226" s="5">
+        <v>3322</v>
+      </c>
       <c r="F4226" s="5">
         <v>12219</v>
       </c>
@@ -75916,6 +75924,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="199" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="f29b0ff1a26a7575c948acee1be83c00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3fe347a261331acec84421138fd81903" ns2:_="">
     <xsd:import namespace="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
@@ -76124,15 +76141,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -76173,6 +76181,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671879E3-B982-4FE4-BADD-85A07701A750}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7A7B58-26E5-466B-854F-C9D5FAFB5E44}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -76186,14 +76202,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671879E3-B982-4FE4-BADD-85A07701A750}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
